--- a/reports/service-tracking-report-WILLYMAY-DE-JESUS-evaluator-cache-serviceTracking-WILLYMAY-DE-JESUS-III-202501-202612.xlsx
+++ b/reports/service-tracking-report-WILLYMAY-DE-JESUS-evaluator-cache-serviceTracking-WILLYMAY-DE-JESUS-III-202501-202612.xlsx
@@ -99,7 +99,7 @@
     <x:t>Radiotelegraphy</x:t>
   </x:si>
   <x:si>
-    <x:t>ANGELICA  VERGARA PANCHITO</x:t>
+    <x:t>ANGELICA VERGARA PANCHITO</x:t>
   </x:si>
   <x:si>
     <x:t>TEMP-ROIII-1007-25</x:t>

--- a/reports/service-tracking-report-WILLYMAY-DE-JESUS-evaluator-cache-serviceTracking-WILLYMAY-DE-JESUS-III-202501-202612.xlsx
+++ b/reports/service-tracking-report-WILLYMAY-DE-JESUS-evaluator-cache-serviceTracking-WILLYMAY-DE-JESUS-III-202501-202612.xlsx
@@ -9,58 +9,22 @@
     <x:sheet name="June 2025" sheetId="7" r:id="rId7"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="Applicants">Sheet1!$A$6:$M$7</x:definedName>
+    <x:definedName name="Applicants">Sheet1!$A$8:$M$9</x:definedName>
     <x:definedName name="summary">#REF!</x:definedName>
   </x:definedNames>
   <x:calcPr/>
   <x:extLst>
     <x:ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="M1zy22YtJ+TLWEM7ow84Ac98JQFmbAbmONakZm1eVcw="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="6Gqj+nP2ZfjBIlYJvjiPFyqmWD9usEriw94U1uDhyO0="/>
     </x:ext>
   </x:extLst>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
-  <x:si>
-    <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Application Type</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPANY NAME / NAME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STATUS(NEW/REN/DUP)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FULL ADDRESS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PERMIT NO.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REFERENCE NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE OF FILING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EXPIRATION DATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OR NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMOUNT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE PAID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BY</x:t>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+  <x:si>
+    <x:t>{{Name}}</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur</x:t>
@@ -136,7 +100,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -163,12 +127,6 @@
     </x:font>
     <x:font>
       <x:b/>
-      <x:sz val="13.0"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
       <x:color theme="1"/>
       <x:name val="Arial"/>
     </x:font>
@@ -176,6 +134,27 @@
       <x:sz val="11.0"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="13.0"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -190,13 +169,6 @@
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -241,12 +213,12 @@
   <x:borders count="14">
     <x:border/>
     <x:border>
-      <x:left style="thin">
-        <x:color rgb="FF000000"/>
-      </x:left>
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
       <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
@@ -258,14 +230,14 @@
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF000000"/>
-      </x:top>
       <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
     </x:border>
     <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF000000"/>
+      </x:left>
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
@@ -447,7 +419,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="25">
+  <x:cellStyleXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -458,190 +430,208 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="33">
+  <x:cellXfs count="36">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="0" shrinkToFit="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="0" shrinkToFit="0" readingOrder="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="0" shrinkToFit="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -905,320 +895,296 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>45809</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
       <x:c r="B6" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s"/>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s"/>
       <x:c r="E6" s="11" t="s">
-        <x:v>15</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>16</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
         <x:v>45826.3053472222</x:v>
       </x:c>
-      <x:c r="I6" s="12">
+      <x:c r="I6" s="13">
         <x:v>45826.3053703704</x:v>
       </x:c>
-      <x:c r="J6" s="11" t="n">
+      <x:c r="J6" s="12" t="n">
         <x:v>1434444</x:v>
       </x:c>
-      <x:c r="K6" s="13" t="n">
+      <x:c r="K6" s="14" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L6" s="12">
+      <x:c r="L6" s="15">
         <x:v>45826.3117939815</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="G7" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="H7" s="12">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="16" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C7" s="16" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D7" s="16" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E7" s="16" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F7" s="16" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G7" s="16" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H7" s="17">
         <x:v>45826.1308796296</x:v>
       </x:c>
-      <x:c r="I7" s="14">
+      <x:c r="I7" s="18">
         <x:v>45826</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="n">
+      <x:c r="J7" s="16" t="n">
         <x:v>2734401</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="n">
+      <x:c r="K7" s="19" t="n">
         <x:v>1052</x:v>
       </x:c>
-      <x:c r="L7" s="12">
+      <x:c r="L7" s="17">
         <x:v>45826.1478935185</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
+      <x:c r="M7" s="16" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B8" s="15" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C8" s="15" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D8" s="16" t="s"/>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="20" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C8" s="20" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D8" s="20" t="s"/>
+      <x:c r="E8" s="20" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F8" s="20" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G8" s="20" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G8" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="21">
         <x:v>45825.2634953704</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="21">
         <x:v>45825.2635300926</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="n">
+      <x:c r="J8" s="20" t="n">
         <x:v>274001</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="22" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="21">
         <x:v>45825.2871759259</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
-        <x:v>18</x:v>
+      <x:c r="M8" s="20" t="s">
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="15" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C9" s="15" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D9" s="16" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E9" s="15" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F9" s="15" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="G9" s="15" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="B9" s="20" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C9" s="20" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D9" s="20" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E9" s="20" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F9" s="20" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G9" s="20" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H9" s="21">
         <x:v>45826.1449768519</x:v>
       </x:c>
-      <x:c r="I9" s="20">
+      <x:c r="I9" s="23">
         <x:v>45826</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="n">
+      <x:c r="J9" s="20" t="n">
         <x:v>1435666</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="22" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="21">
         <x:v>45826.2821412037</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
-        <x:v>18</x:v>
+      <x:c r="M9" s="20" t="s">
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="21" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="23" t="s"/>
-      <x:c r="F12" s="23" t="s"/>
+      <x:c r="B12" s="24" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C12" s="25" t="s"/>
+      <x:c r="D12" s="25" t="s"/>
+      <x:c r="E12" s="26" t="s"/>
+      <x:c r="F12" s="26" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="24" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C13" s="25" t="s"/>
-      <x:c r="D13" s="25" t="s"/>
-      <x:c r="E13" s="25" t="s"/>
-      <x:c r="F13" s="26" t="s">
-        <x:v>33</x:v>
+      <x:c r="B13" s="27" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C13" s="28" t="s"/>
+      <x:c r="D13" s="28" t="s"/>
+      <x:c r="E13" s="28" t="s"/>
+      <x:c r="F13" s="29" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C14" s="28" t="s"/>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="28" t="s"/>
-      <x:c r="F14" s="29" t="n">
+      <x:c r="B14" s="30" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C14" s="31" t="s"/>
+      <x:c r="D14" s="31" t="s"/>
+      <x:c r="E14" s="31" t="s"/>
+      <x:c r="F14" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="27" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C15" s="28" t="s"/>
-      <x:c r="D15" s="28" t="s"/>
-      <x:c r="E15" s="28" t="s"/>
-      <x:c r="F15" s="29" t="n">
+      <x:c r="B15" s="30" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C15" s="31" t="s"/>
+      <x:c r="D15" s="31" t="s"/>
+      <x:c r="E15" s="31" t="s"/>
+      <x:c r="F15" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="27" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C16" s="28" t="s"/>
-      <x:c r="D16" s="28" t="s"/>
-      <x:c r="E16" s="28" t="s"/>
-      <x:c r="F16" s="29" t="n">
+      <x:c r="B16" s="30" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C16" s="31" t="s"/>
+      <x:c r="D16" s="31" t="s"/>
+      <x:c r="E16" s="31" t="s"/>
+      <x:c r="F16" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="27" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C17" s="28" t="s"/>
-      <x:c r="D17" s="28" t="s"/>
-      <x:c r="E17" s="28" t="s"/>
-      <x:c r="F17" s="29" t="n">
+      <x:c r="B17" s="30" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C17" s="31" t="s"/>
+      <x:c r="D17" s="31" t="s"/>
+      <x:c r="E17" s="31" t="s"/>
+      <x:c r="F17" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="30" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C18" s="31" t="s"/>
-      <x:c r="D18" s="31" t="s"/>
-      <x:c r="E18" s="31" t="s"/>
-      <x:c r="F18" s="32" t="n">
+      <x:c r="B18" s="33" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C18" s="34" t="s"/>
+      <x:c r="D18" s="34" t="s"/>
+      <x:c r="E18" s="34" t="s"/>
+      <x:c r="F18" s="35" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-WILLYMAY-DE-JESUS-evaluator-cache-serviceTracking-WILLYMAY-DE-JESUS-III-202501-202612.xlsx
+++ b/reports/service-tracking-report-WILLYMAY-DE-JESUS-evaluator-cache-serviceTracking-WILLYMAY-DE-JESUS-III-202501-202612.xlsx
@@ -22,9 +22,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
-  <x:si>
-    <x:t>{{Name}}</x:t>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+  <x:si>
+    <x:t>EVALUATOR SUMMARY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WILLYMAY DE JESUS</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur</x:t>
@@ -500,7 +503,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="36">
+  <x:cellXfs count="37">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -536,39 +539,39 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="14" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -585,6 +588,10 @@
     </x:xf>
     <x:xf numFmtId="14" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -880,7 +887,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -897,7 +906,7 @@
     <x:row r="3" spans="1:28">
       <x:c r="A3" s="3" t="s"/>
       <x:c r="B3" s="3">
-        <x:v>45809</x:v>
+        <x:v>46082</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s"/>
       <x:c r="D3" s="3" t="s"/>
@@ -958,22 +967,22 @@
       <x:c r="AA5" s="5" t="s"/>
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B6" s="11" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D6" s="12" t="s"/>
       <x:c r="E6" s="11" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H6" s="13">
         <x:v>45826.3053472222</x:v>
@@ -991,30 +1000,30 @@
         <x:v>45826.3117939815</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C7" s="16" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D7" s="16" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E7" s="16" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F7" s="16" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G7" s="16" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H7" s="17">
         <x:v>45826.1308796296</x:v>
@@ -1032,27 +1041,27 @@
         <x:v>45826.1478935185</x:v>
       </x:c>
       <x:c r="M7" s="16" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="20" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C8" s="20" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D8" s="20" t="s"/>
       <x:c r="E8" s="20" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F8" s="20" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G8" s="20" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H8" s="21">
         <x:v>45825.2634953704</x:v>
@@ -1070,27 +1079,27 @@
         <x:v>45825.2871759259</x:v>
       </x:c>
       <x:c r="M8" s="20" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B9" s="20" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C9" s="20" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D9" s="20" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E9" s="20" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F9" s="20" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G9" s="20" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H9" s="21">
         <x:v>45826.1449768519</x:v>
@@ -1108,88 +1117,114 @@
         <x:v>45826.2821412037</x:v>
       </x:c>
       <x:c r="M9" s="20" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="24" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C12" s="25" t="s"/>
-      <x:c r="D12" s="25" t="s"/>
-      <x:c r="E12" s="26" t="s"/>
-      <x:c r="F12" s="26" t="s"/>
+    <x:row r="10" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B10" s="24" t="s"/>
+      <x:c r="C10" s="24" t="s"/>
+      <x:c r="D10" s="24" t="s"/>
+      <x:c r="E10" s="24" t="s"/>
+      <x:c r="F10" s="24" t="s"/>
+      <x:c r="G10" s="24" t="s"/>
+      <x:c r="H10" s="24" t="s"/>
+      <x:c r="I10" s="24" t="s"/>
+      <x:c r="J10" s="24" t="s"/>
+      <x:c r="K10" s="24" t="s"/>
+      <x:c r="L10" s="24" t="s"/>
+      <x:c r="M10" s="24" t="s"/>
     </x:row>
-    <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="27" t="s">
+    <x:row r="11" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B11" s="24" t="s"/>
+      <x:c r="C11" s="24" t="s"/>
+      <x:c r="D11" s="24" t="s"/>
+      <x:c r="E11" s="24" t="s"/>
+      <x:c r="F11" s="24" t="s"/>
+      <x:c r="G11" s="24" t="s"/>
+      <x:c r="H11" s="24" t="s"/>
+      <x:c r="I11" s="24" t="s"/>
+      <x:c r="J11" s="24" t="s"/>
+      <x:c r="K11" s="24" t="s"/>
+      <x:c r="L11" s="24" t="s"/>
+      <x:c r="M11" s="24" t="s"/>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B14" s="25" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C13" s="28" t="s"/>
-      <x:c r="D13" s="28" t="s"/>
-      <x:c r="E13" s="28" t="s"/>
-      <x:c r="F13" s="29" t="s">
+      <x:c r="C14" s="26" t="s"/>
+      <x:c r="D14" s="26" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="27" t="s"/>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B15" s="28" t="s">
         <x:v>21</x:v>
       </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="30" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C14" s="31" t="s"/>
-      <x:c r="D14" s="31" t="s"/>
-      <x:c r="E14" s="31" t="s"/>
-      <x:c r="F14" s="32" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="30" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C15" s="31" t="s"/>
-      <x:c r="D15" s="31" t="s"/>
-      <x:c r="E15" s="31" t="s"/>
-      <x:c r="F15" s="32" t="n">
-        <x:v>1</x:v>
+      <x:c r="C15" s="29" t="s"/>
+      <x:c r="D15" s="29" t="s"/>
+      <x:c r="E15" s="29" t="s"/>
+      <x:c r="F15" s="30" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="30" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C16" s="31" t="s"/>
-      <x:c r="D16" s="31" t="s"/>
-      <x:c r="E16" s="31" t="s"/>
-      <x:c r="F16" s="32" t="n">
+      <x:c r="B16" s="31" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C16" s="32" t="s"/>
+      <x:c r="D16" s="32" t="s"/>
+      <x:c r="E16" s="32" t="s"/>
+      <x:c r="F16" s="33" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="30" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C17" s="31" t="s"/>
-      <x:c r="D17" s="31" t="s"/>
-      <x:c r="E17" s="31" t="s"/>
-      <x:c r="F17" s="32" t="n">
+      <x:c r="B17" s="31" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C17" s="32" t="s"/>
+      <x:c r="D17" s="32" t="s"/>
+      <x:c r="E17" s="32" t="s"/>
+      <x:c r="F17" s="33" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="33" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C18" s="34" t="s"/>
-      <x:c r="D18" s="34" t="s"/>
-      <x:c r="E18" s="34" t="s"/>
-      <x:c r="F18" s="35" t="n">
+    <x:row r="18" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B18" s="31" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C18" s="32" t="s"/>
+      <x:c r="D18" s="32" t="s"/>
+      <x:c r="E18" s="32" t="s"/>
+      <x:c r="F18" s="33" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B19" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C19" s="32" t="s"/>
+      <x:c r="D19" s="32" t="s"/>
+      <x:c r="E19" s="32" t="s"/>
+      <x:c r="F19" s="33" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B20" s="34" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C20" s="35" t="s"/>
+      <x:c r="D20" s="35" t="s"/>
+      <x:c r="E20" s="35" t="s"/>
+      <x:c r="F20" s="36" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2164,16 +2199,17 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="9">
-    <x:mergeCell ref="B1:M2"/>
-    <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B12:F12"/>
-    <x:mergeCell ref="B13:E13"/>
-    <x:mergeCell ref="B14:E14"/>
+  <x:mergeCells count="10">
+    <x:mergeCell ref="B1:M1"/>
+    <x:mergeCell ref="B2:M2"/>
+    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B14:F14"/>
     <x:mergeCell ref="B15:E15"/>
     <x:mergeCell ref="B16:E16"/>
     <x:mergeCell ref="B17:E17"/>
     <x:mergeCell ref="B18:E18"/>
+    <x:mergeCell ref="B19:E19"/>
+    <x:mergeCell ref="B20:E20"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-WILLYMAY-DE-JESUS-evaluator-cache-serviceTracking-WILLYMAY-DE-JESUS-III-202501-202612.xlsx
+++ b/reports/service-tracking-report-WILLYMAY-DE-JESUS-evaluator-cache-serviceTracking-WILLYMAY-DE-JESUS-III-202501-202612.xlsx
@@ -937,7 +937,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -1005,7 +1005,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s">
         <x:v>8</x:v>

--- a/reports/service-tracking-report-WILLYMAY-DE-JESUS-evaluator-cache-serviceTracking-WILLYMAY-DE-JESUS-III-202501-202612.xlsx
+++ b/reports/service-tracking-report-WILLYMAY-DE-JESUS-evaluator-cache-serviceTracking-WILLYMAY-DE-JESUS-III-202501-202612.xlsx
@@ -22,12 +22,48 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
   <x:si>
     <x:t>WILLYMAY DE JESUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Application Type</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPANY NAME / NAME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STATUS(NEW/REN/DUP)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FULL ADDRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PERMIT NO.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REFERENCE NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE OF FILING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EXPIRATION DATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OR NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMOUNT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE PAID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BY</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur</x:t>
@@ -103,7 +139,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -148,21 +184,6 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
@@ -172,6 +193,13 @@
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -422,7 +450,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="27">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -433,77 +461,71 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="33">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -534,111 +556,95 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -939,18 +945,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -968,260 +962,272 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s"/>
-      <x:c r="E6" s="11" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>45826.3053472222</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>45826.3053703704</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1434444</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L6" s="15">
-        <x:v>45826.3117939815</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>7</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="16" t="s">
+      <x:c r="B7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C7" s="16" t="s">
+      <x:c r="I7" s="10" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="D7" s="16" t="s">
+      <x:c r="J7" s="10" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="E7" s="16" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F7" s="16" t="s">
+      <x:c r="K7" s="10" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="G7" s="16" t="s">
+      <x:c r="L7" s="10" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="H7" s="17">
-        <x:v>45826.1308796296</x:v>
-      </x:c>
-      <x:c r="I7" s="18">
-        <x:v>45826</x:v>
-      </x:c>
-      <x:c r="J7" s="16" t="n">
-        <x:v>2734401</x:v>
-      </x:c>
-      <x:c r="K7" s="19" t="n">
-        <x:v>1052</x:v>
-      </x:c>
-      <x:c r="L7" s="17">
-        <x:v>45826.1478935185</x:v>
-      </x:c>
-      <x:c r="M7" s="16" t="s">
-        <x:v>7</x:v>
+      <x:c r="M7" s="10" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="20" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="20" t="s">
+      <x:c r="B8" s="11" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D8" s="20" t="s"/>
-      <x:c r="E8" s="20" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F8" s="20" t="s">
+      <x:c r="C8" s="11" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="G8" s="20" t="s">
+      <x:c r="D8" s="11" t="s"/>
+      <x:c r="E8" s="11" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="H8" s="21">
-        <x:v>45825.2634953704</x:v>
-      </x:c>
-      <x:c r="I8" s="21">
-        <x:v>45825.2635300926</x:v>
-      </x:c>
-      <x:c r="J8" s="20" t="n">
-        <x:v>274001</x:v>
-      </x:c>
-      <x:c r="K8" s="22" t="n">
+      <x:c r="F8" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>45826.3053472222</x:v>
+      </x:c>
+      <x:c r="I8" s="12">
+        <x:v>45826.3053703704</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1434444</x:v>
+      </x:c>
+      <x:c r="K8" s="13" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L8" s="21">
-        <x:v>45825.2871759259</x:v>
-      </x:c>
-      <x:c r="M8" s="20" t="s">
-        <x:v>7</x:v>
+      <x:c r="L8" s="12">
+        <x:v>45826.3117939815</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="20" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C9" s="20" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D9" s="20" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="E9" s="20" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F9" s="20" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="G9" s="20" t="s">
+      <x:c r="B9" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>45826.1308796296</x:v>
+      </x:c>
+      <x:c r="I9" s="14">
+        <x:v>45826</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>2734401</x:v>
+      </x:c>
+      <x:c r="K9" s="13" t="n">
+        <x:v>1052</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>45826.1478935185</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H9" s="21">
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s"/>
+      <x:c r="E10" s="15" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
+        <x:v>45825.2634953704</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>45825.2635300926</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="n">
+        <x:v>274001</x:v>
+      </x:c>
+      <x:c r="K10" s="18" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L10" s="19">
+        <x:v>45825.2871759259</x:v>
+      </x:c>
+      <x:c r="M10" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
         <x:v>45826.1449768519</x:v>
       </x:c>
-      <x:c r="I9" s="23">
+      <x:c r="I11" s="20">
         <x:v>45826</x:v>
       </x:c>
-      <x:c r="J9" s="20" t="n">
+      <x:c r="J11" s="16" t="n">
         <x:v>1435666</x:v>
       </x:c>
-      <x:c r="K9" s="22" t="n">
+      <x:c r="K11" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L9" s="21">
+      <x:c r="L11" s="19">
         <x:v>45826.2821412037</x:v>
       </x:c>
-      <x:c r="M9" s="20" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B10" s="24" t="s"/>
-      <x:c r="C10" s="24" t="s"/>
-      <x:c r="D10" s="24" t="s"/>
-      <x:c r="E10" s="24" t="s"/>
-      <x:c r="F10" s="24" t="s"/>
-      <x:c r="G10" s="24" t="s"/>
-      <x:c r="H10" s="24" t="s"/>
-      <x:c r="I10" s="24" t="s"/>
-      <x:c r="J10" s="24" t="s"/>
-      <x:c r="K10" s="24" t="s"/>
-      <x:c r="L10" s="24" t="s"/>
-      <x:c r="M10" s="24" t="s"/>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B11" s="24" t="s"/>
-      <x:c r="C11" s="24" t="s"/>
-      <x:c r="D11" s="24" t="s"/>
-      <x:c r="E11" s="24" t="s"/>
-      <x:c r="F11" s="24" t="s"/>
-      <x:c r="G11" s="24" t="s"/>
-      <x:c r="H11" s="24" t="s"/>
-      <x:c r="I11" s="24" t="s"/>
-      <x:c r="J11" s="24" t="s"/>
-      <x:c r="K11" s="24" t="s"/>
-      <x:c r="L11" s="24" t="s"/>
-      <x:c r="M11" s="24" t="s"/>
+      <x:c r="M11" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="25" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C14" s="26" t="s"/>
-      <x:c r="D14" s="26" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="27" t="s"/>
+      <x:c r="B14" s="21" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C14" s="22" t="s"/>
+      <x:c r="D14" s="22" t="s"/>
+      <x:c r="E14" s="23" t="s"/>
+      <x:c r="F14" s="23" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="28" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C15" s="29" t="s"/>
-      <x:c r="D15" s="29" t="s"/>
-      <x:c r="E15" s="29" t="s"/>
-      <x:c r="F15" s="30" t="s">
-        <x:v>22</x:v>
+      <x:c r="B15" s="24" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C15" s="25" t="s"/>
+      <x:c r="D15" s="25" t="s"/>
+      <x:c r="E15" s="25" t="s"/>
+      <x:c r="F15" s="26" t="s">
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="31" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C16" s="32" t="s"/>
-      <x:c r="D16" s="32" t="s"/>
-      <x:c r="E16" s="32" t="s"/>
-      <x:c r="F16" s="33" t="n">
+      <x:c r="B16" s="27" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C16" s="28" t="s"/>
+      <x:c r="D16" s="28" t="s"/>
+      <x:c r="E16" s="28" t="s"/>
+      <x:c r="F16" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="31" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C17" s="32" t="s"/>
-      <x:c r="D17" s="32" t="s"/>
-      <x:c r="E17" s="32" t="s"/>
-      <x:c r="F17" s="33" t="n">
+      <x:c r="B17" s="27" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C17" s="28" t="s"/>
+      <x:c r="D17" s="28" t="s"/>
+      <x:c r="E17" s="28" t="s"/>
+      <x:c r="F17" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="31" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C18" s="32" t="s"/>
-      <x:c r="D18" s="32" t="s"/>
-      <x:c r="E18" s="32" t="s"/>
-      <x:c r="F18" s="33" t="n">
+      <x:c r="B18" s="27" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C18" s="28" t="s"/>
+      <x:c r="D18" s="28" t="s"/>
+      <x:c r="E18" s="28" t="s"/>
+      <x:c r="F18" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="31" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C19" s="32" t="s"/>
-      <x:c r="D19" s="32" t="s"/>
-      <x:c r="E19" s="32" t="s"/>
-      <x:c r="F19" s="33" t="n">
+      <x:c r="B19" s="27" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C19" s="28" t="s"/>
+      <x:c r="D19" s="28" t="s"/>
+      <x:c r="E19" s="28" t="s"/>
+      <x:c r="F19" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B20" s="34" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C20" s="35" t="s"/>
-      <x:c r="D20" s="35" t="s"/>
-      <x:c r="E20" s="35" t="s"/>
-      <x:c r="F20" s="36" t="n">
+      <x:c r="B20" s="30" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C20" s="31" t="s"/>
+      <x:c r="D20" s="31" t="s"/>
+      <x:c r="E20" s="31" t="s"/>
+      <x:c r="F20" s="32" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-WILLYMAY-DE-JESUS-evaluator-cache-serviceTracking-WILLYMAY-DE-JESUS-III-202501-202612.xlsx
+++ b/reports/service-tracking-report-WILLYMAY-DE-JESUS-evaluator-cache-serviceTracking-WILLYMAY-DE-JESUS-III-202501-202612.xlsx
@@ -22,12 +22,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
   <x:si>
     <x:t>WILLYMAY DE JESUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>III | June 2025</x:t>
   </x:si>
   <x:si>
     <x:t>Application Type</x:t>
@@ -139,7 +142,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="15">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -179,6 +182,30 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="16"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -450,14 +477,23 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="25">
+  <x:cellStyleXfs count="28">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -470,62 +506,62 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="33">
+  <x:cellXfs count="36">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -556,95 +592,107 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -873,58 +921,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="B2" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -967,267 +1015,267 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s"/>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="D8" s="14" t="s"/>
+      <x:c r="E8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="G8" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>45826.3053472222</x:v>
       </x:c>
-      <x:c r="I8" s="12">
+      <x:c r="I8" s="15">
         <x:v>45826.3053703704</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1434444</x:v>
       </x:c>
-      <x:c r="K8" s="13" t="n">
+      <x:c r="K8" s="16" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="15">
         <x:v>45826.3117939815</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
-        <x:v>19</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
+      <x:c r="B9" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
+        <x:v>45826.1308796296</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>45826</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>2734401</x:v>
+      </x:c>
+      <x:c r="K9" s="16" t="n">
+        <x:v>1052</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>45826.1478935185</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="C9" s="11" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D9" s="11" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E9" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="F9" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="G9" s="11" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H9" s="12">
-        <x:v>45826.1308796296</x:v>
-      </x:c>
-      <x:c r="I9" s="14">
-        <x:v>45826</x:v>
-      </x:c>
-      <x:c r="J9" s="11" t="n">
-        <x:v>2734401</x:v>
-      </x:c>
-      <x:c r="K9" s="13" t="n">
-        <x:v>1052</x:v>
-      </x:c>
-      <x:c r="L9" s="12">
-        <x:v>45826.1478935185</x:v>
-      </x:c>
-      <x:c r="M9" s="11" t="s">
-        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="B10" s="18" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s"/>
-      <x:c r="E10" s="15" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="C10" s="18" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="D10" s="19" t="s"/>
+      <x:c r="E10" s="18" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F10" s="18" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="G10" s="18" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="H10" s="20">
         <x:v>45825.2634953704</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="20">
         <x:v>45825.2635300926</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="n">
+      <x:c r="J10" s="19" t="n">
         <x:v>274001</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="21" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="22">
         <x:v>45825.2871759259</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>19</x:v>
+      <x:c r="M10" s="18" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="B11" s="18" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C11" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="F11" s="15" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="D11" s="19" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E11" s="18" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F11" s="18" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="G11" s="18" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H11" s="20">
         <x:v>45826.1449768519</x:v>
       </x:c>
-      <x:c r="I11" s="20">
+      <x:c r="I11" s="23">
         <x:v>45826</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="n">
+      <x:c r="J11" s="19" t="n">
         <x:v>1435666</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="21" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="22">
         <x:v>45826.2821412037</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
-        <x:v>19</x:v>
+      <x:c r="M11" s="18" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="21" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C14" s="22" t="s"/>
-      <x:c r="D14" s="22" t="s"/>
-      <x:c r="E14" s="23" t="s"/>
-      <x:c r="F14" s="23" t="s"/>
+      <x:c r="B14" s="24" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C14" s="25" t="s"/>
+      <x:c r="D14" s="25" t="s"/>
+      <x:c r="E14" s="26" t="s"/>
+      <x:c r="F14" s="26" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="24" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C15" s="25" t="s"/>
-      <x:c r="D15" s="25" t="s"/>
-      <x:c r="E15" s="25" t="s"/>
-      <x:c r="F15" s="26" t="s">
+      <x:c r="B15" s="27" t="s">
         <x:v>34</x:v>
+      </x:c>
+      <x:c r="C15" s="28" t="s"/>
+      <x:c r="D15" s="28" t="s"/>
+      <x:c r="E15" s="28" t="s"/>
+      <x:c r="F15" s="29" t="s">
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="27" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C16" s="28" t="s"/>
-      <x:c r="D16" s="28" t="s"/>
-      <x:c r="E16" s="28" t="s"/>
-      <x:c r="F16" s="29" t="n">
+      <x:c r="B16" s="30" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C16" s="31" t="s"/>
+      <x:c r="D16" s="31" t="s"/>
+      <x:c r="E16" s="31" t="s"/>
+      <x:c r="F16" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="27" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C17" s="28" t="s"/>
-      <x:c r="D17" s="28" t="s"/>
-      <x:c r="E17" s="28" t="s"/>
-      <x:c r="F17" s="29" t="n">
+      <x:c r="B17" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C17" s="31" t="s"/>
+      <x:c r="D17" s="31" t="s"/>
+      <x:c r="E17" s="31" t="s"/>
+      <x:c r="F17" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="27" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C18" s="28" t="s"/>
-      <x:c r="D18" s="28" t="s"/>
-      <x:c r="E18" s="28" t="s"/>
-      <x:c r="F18" s="29" t="n">
+      <x:c r="B18" s="30" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C18" s="31" t="s"/>
+      <x:c r="D18" s="31" t="s"/>
+      <x:c r="E18" s="31" t="s"/>
+      <x:c r="F18" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="27" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C19" s="28" t="s"/>
-      <x:c r="D19" s="28" t="s"/>
-      <x:c r="E19" s="28" t="s"/>
-      <x:c r="F19" s="29" t="n">
+      <x:c r="B19" s="30" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C19" s="31" t="s"/>
+      <x:c r="D19" s="31" t="s"/>
+      <x:c r="E19" s="31" t="s"/>
+      <x:c r="F19" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B20" s="30" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C20" s="31" t="s"/>
-      <x:c r="D20" s="31" t="s"/>
-      <x:c r="E20" s="31" t="s"/>
-      <x:c r="F20" s="32" t="n">
+      <x:c r="B20" s="33" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C20" s="34" t="s"/>
+      <x:c r="D20" s="34" t="s"/>
+      <x:c r="E20" s="34" t="s"/>
+      <x:c r="F20" s="35" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -2208,7 +2256,7 @@
   <x:mergeCells count="10">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B14:F14"/>
     <x:mergeCell ref="B15:E15"/>
     <x:mergeCell ref="B16:E16"/>

--- a/reports/service-tracking-report-WILLYMAY-DE-JESUS-evaluator-cache-serviceTracking-WILLYMAY-DE-JESUS-III-202501-202612.xlsx
+++ b/reports/service-tracking-report-WILLYMAY-DE-JESUS-evaluator-cache-serviceTracking-WILLYMAY-DE-JESUS-III-202501-202612.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -67,6 +67,42 @@
   </x:si>
   <x:si>
     <x:t>BY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ApplicationType}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Name}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Status}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Address}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.PermitNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ReferenceNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.DateOfFiling}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ExpirationDate}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ORNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Amount}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.DatePaid}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ORBy}}</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur</x:t>
@@ -139,10 +175,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="3">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
+    <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
+    <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="15">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -187,15 +225,7 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="16"/>
-      <x:color rgb="FF0000FF"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF0000FF"/>
+      <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
@@ -211,15 +241,8 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -477,26 +500,26 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="28">
+  <x:cellStyleXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -506,62 +529,59 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="36">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -592,107 +612,91 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -921,78 +925,90 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="28" customHeight="1">
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="10" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C1" s="10" t="s"/>
-      <x:c r="D1" s="10" t="s"/>
-      <x:c r="E1" s="10" t="s"/>
-      <x:c r="F1" s="10" t="s"/>
-      <x:c r="G1" s="10" t="s"/>
-      <x:c r="H1" s="10" t="s"/>
-      <x:c r="I1" s="10" t="s"/>
-      <x:c r="J1" s="10" t="s"/>
-      <x:c r="K1" s="10" t="s"/>
-      <x:c r="L1" s="10" t="s"/>
-      <x:c r="M1" s="10" t="s"/>
+      <x:c r="B1" s="1" t="s"/>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="22" customHeight="1">
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="11" t="s"/>
-      <x:c r="D2" s="11" t="s"/>
-      <x:c r="E2" s="11" t="s"/>
-      <x:c r="F2" s="11" t="s"/>
-      <x:c r="G2" s="11" t="s"/>
-      <x:c r="H2" s="11" t="s"/>
-      <x:c r="I2" s="11" t="s"/>
-      <x:c r="J2" s="11" t="s"/>
-      <x:c r="K2" s="11" t="s"/>
-      <x:c r="L2" s="11" t="s"/>
-      <x:c r="M2" s="11" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28" ht="22" customHeight="1">
+    <x:row r="3" spans="1:28" ht="28" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="12" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="12" t="s"/>
-      <x:c r="D3" s="12" t="s"/>
-      <x:c r="E3" s="12" t="s"/>
-      <x:c r="F3" s="12" t="s"/>
-      <x:c r="G3" s="12" t="s"/>
-      <x:c r="H3" s="12" t="s"/>
-      <x:c r="I3" s="12" t="s"/>
-      <x:c r="J3" s="12" t="s"/>
-      <x:c r="K3" s="12" t="s"/>
-      <x:c r="L3" s="12" t="s"/>
-      <x:c r="M3" s="12" t="s"/>
+      <x:c r="B3" s="10" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="s"/>
+      <x:c r="D3" s="10" t="s"/>
+      <x:c r="E3" s="10" t="s"/>
+      <x:c r="F3" s="10" t="s"/>
+      <x:c r="G3" s="10" t="s"/>
+      <x:c r="H3" s="10" t="s"/>
+      <x:c r="I3" s="10" t="s"/>
+      <x:c r="J3" s="10" t="s"/>
+      <x:c r="K3" s="10" t="s"/>
+      <x:c r="L3" s="10" t="s"/>
+      <x:c r="M3" s="10" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
-    <x:row r="4" spans="1:28">
+    <x:row r="4" spans="1:28" ht="22" customHeight="1">
       <x:c r="A4" s="3" t="s"/>
-      <x:c r="B4" s="3" t="s"/>
-      <x:c r="C4" s="3" t="s"/>
-      <x:c r="D4" s="3" t="s"/>
-      <x:c r="E4" s="3" t="s"/>
-      <x:c r="F4" s="3" t="s"/>
-      <x:c r="G4" s="3" t="s"/>
-      <x:c r="H4" s="3" t="s"/>
-      <x:c r="I4" s="3" t="s"/>
-      <x:c r="J4" s="3" t="s"/>
-      <x:c r="K4" s="3" t="s"/>
-      <x:c r="L4" s="3" t="s"/>
-      <x:c r="M4" s="3" t="s"/>
+      <x:c r="B4" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="s"/>
+      <x:c r="D4" s="11" t="s"/>
+      <x:c r="E4" s="11" t="s"/>
+      <x:c r="F4" s="11" t="s"/>
+      <x:c r="G4" s="11" t="s"/>
+      <x:c r="H4" s="11" t="s"/>
+      <x:c r="I4" s="11" t="s"/>
+      <x:c r="J4" s="11" t="s"/>
+      <x:c r="K4" s="11" t="s"/>
+      <x:c r="L4" s="11" t="s"/>
+      <x:c r="M4" s="11" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28">
+    <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="12" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C5" s="12" t="s"/>
+      <x:c r="D5" s="12" t="s"/>
+      <x:c r="E5" s="12" t="s"/>
+      <x:c r="F5" s="12" t="s"/>
+      <x:c r="G5" s="12" t="s"/>
+      <x:c r="H5" s="12" t="s"/>
+      <x:c r="I5" s="12" t="s"/>
+      <x:c r="J5" s="12" t="s"/>
+      <x:c r="K5" s="12" t="s"/>
+      <x:c r="L5" s="12" t="s"/>
+      <x:c r="M5" s="12" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1013,7 +1029,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1053,234 +1069,284 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="9" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="C8" s="9" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s"/>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="D8" s="9" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="E8" s="9" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="F8" s="9" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="15">
-        <x:v>45826.3053472222</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
-        <x:v>45826.3053703704</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1434444</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L8" s="15">
-        <x:v>45826.3117939815</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
+      <x:c r="G8" s="9" t="s">
         <x:v>20</x:v>
       </x:c>
+      <x:c r="H8" s="9" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I8" s="9" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J8" s="9" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="K8" s="9" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="L8" s="9" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="M8" s="9" t="s">
+        <x:v>26</x:v>
+      </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>45826.1308796296</x:v>
-      </x:c>
-      <x:c r="I9" s="17">
-        <x:v>45826</x:v>
-      </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>2734401</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
-        <x:v>1052</x:v>
-      </x:c>
-      <x:c r="L9" s="15">
-        <x:v>45826.1478935185</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
+    <x:row r="9" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B9" s="14" t="s"/>
+      <x:c r="C9" s="14" t="s"/>
+      <x:c r="D9" s="14" t="s"/>
+      <x:c r="E9" s="14" t="s"/>
+      <x:c r="F9" s="14" t="s"/>
+      <x:c r="G9" s="14" t="s"/>
+      <x:c r="H9" s="14" t="s"/>
+      <x:c r="I9" s="14" t="s"/>
+      <x:c r="J9" s="14" t="s"/>
+      <x:c r="K9" s="14" t="s"/>
+      <x:c r="L9" s="14" t="s"/>
+      <x:c r="M9" s="14" t="s"/>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="18" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C10" s="18" t="s">
+      <x:c r="B10" s="15" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="D10" s="19" t="s"/>
-      <x:c r="E10" s="18" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F10" s="18" t="s">
+      <x:c r="C10" s="15" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="G10" s="18" t="s">
+      <x:c r="D10" s="16" t="s"/>
+      <x:c r="E10" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="H10" s="20">
-        <x:v>45825.2634953704</x:v>
-      </x:c>
-      <x:c r="I10" s="20">
-        <x:v>45825.2635300926</x:v>
-      </x:c>
-      <x:c r="J10" s="19" t="n">
-        <x:v>274001</x:v>
-      </x:c>
-      <x:c r="K10" s="21" t="n">
+      <x:c r="F10" s="15" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
+        <x:v>45826.3053472222</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>45826.3053703704</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="n">
+        <x:v>1434444</x:v>
+      </x:c>
+      <x:c r="K10" s="18" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L10" s="22">
-        <x:v>45825.2871759259</x:v>
-      </x:c>
-      <x:c r="M10" s="18" t="s">
-        <x:v>20</x:v>
+      <x:c r="L10" s="19">
+        <x:v>45826.3117939815</x:v>
+      </x:c>
+      <x:c r="M10" s="15" t="s">
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="18" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C11" s="18" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D11" s="19" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="E11" s="18" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F11" s="18" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G11" s="18" t="s">
+      <x:c r="B11" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
+        <x:v>45826.1308796296</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>45826</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="n">
+        <x:v>2734401</x:v>
+      </x:c>
+      <x:c r="K11" s="18" t="n">
+        <x:v>1052</x:v>
+      </x:c>
+      <x:c r="L11" s="19">
+        <x:v>45826.1478935185</x:v>
+      </x:c>
+      <x:c r="M11" s="15" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="H11" s="20">
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="15" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D12" s="16" t="s"/>
+      <x:c r="E12" s="15" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F12" s="15" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G12" s="15" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H12" s="17">
+        <x:v>45825.2634953704</x:v>
+      </x:c>
+      <x:c r="I12" s="17">
+        <x:v>45825.2635300926</x:v>
+      </x:c>
+      <x:c r="J12" s="16" t="n">
+        <x:v>274001</x:v>
+      </x:c>
+      <x:c r="K12" s="18" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L12" s="19">
+        <x:v>45825.2871759259</x:v>
+      </x:c>
+      <x:c r="M12" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C13" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D13" s="16" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E13" s="15" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F13" s="15" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G13" s="15" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H13" s="17">
         <x:v>45826.1449768519</x:v>
       </x:c>
-      <x:c r="I11" s="23">
+      <x:c r="I13" s="17">
         <x:v>45826</x:v>
       </x:c>
-      <x:c r="J11" s="19" t="n">
+      <x:c r="J13" s="16" t="n">
         <x:v>1435666</x:v>
       </x:c>
-      <x:c r="K11" s="21" t="n">
+      <x:c r="K13" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L11" s="22">
+      <x:c r="L13" s="19">
         <x:v>45826.2821412037</x:v>
       </x:c>
-      <x:c r="M11" s="18" t="s">
-        <x:v>20</x:v>
+      <x:c r="M13" s="15" t="s">
+        <x:v>32</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="24" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C14" s="25" t="s"/>
-      <x:c r="D14" s="25" t="s"/>
-      <x:c r="E14" s="26" t="s"/>
-      <x:c r="F14" s="26" t="s"/>
+    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B16" s="20" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C16" s="21" t="s"/>
+      <x:c r="D16" s="21" t="s"/>
+      <x:c r="E16" s="22" t="s"/>
+      <x:c r="F16" s="22" t="s"/>
     </x:row>
-    <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="27" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C15" s="28" t="s"/>
-      <x:c r="D15" s="28" t="s"/>
-      <x:c r="E15" s="28" t="s"/>
-      <x:c r="F15" s="29" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="30" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C16" s="31" t="s"/>
-      <x:c r="D16" s="31" t="s"/>
-      <x:c r="E16" s="31" t="s"/>
-      <x:c r="F16" s="32" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="30" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C17" s="31" t="s"/>
-      <x:c r="D17" s="31" t="s"/>
-      <x:c r="E17" s="31" t="s"/>
-      <x:c r="F17" s="32" t="n">
-        <x:v>1</x:v>
+    <x:row r="17" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B17" s="23" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C17" s="24" t="s"/>
+      <x:c r="D17" s="24" t="s"/>
+      <x:c r="E17" s="24" t="s"/>
+      <x:c r="F17" s="25" t="s">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="30" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C18" s="31" t="s"/>
-      <x:c r="D18" s="31" t="s"/>
-      <x:c r="E18" s="31" t="s"/>
-      <x:c r="F18" s="32" t="n">
+      <x:c r="B18" s="26" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C18" s="27" t="s"/>
+      <x:c r="D18" s="27" t="s"/>
+      <x:c r="E18" s="27" t="s"/>
+      <x:c r="F18" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="30" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C19" s="31" t="s"/>
-      <x:c r="D19" s="31" t="s"/>
-      <x:c r="E19" s="31" t="s"/>
-      <x:c r="F19" s="32" t="n">
+      <x:c r="B19" s="26" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C19" s="27" t="s"/>
+      <x:c r="D19" s="27" t="s"/>
+      <x:c r="E19" s="27" t="s"/>
+      <x:c r="F19" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B20" s="33" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C20" s="34" t="s"/>
-      <x:c r="D20" s="34" t="s"/>
-      <x:c r="E20" s="34" t="s"/>
-      <x:c r="F20" s="35" t="n">
+    <x:row r="20" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B20" s="26" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C20" s="27" t="s"/>
+      <x:c r="D20" s="27" t="s"/>
+      <x:c r="E20" s="27" t="s"/>
+      <x:c r="F20" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B21" s="26" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C21" s="27" t="s"/>
+      <x:c r="D21" s="27" t="s"/>
+      <x:c r="E21" s="27" t="s"/>
+      <x:c r="F21" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B22" s="29" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C22" s="30" t="s"/>
+      <x:c r="D22" s="30" t="s"/>
+      <x:c r="E22" s="30" t="s"/>
+      <x:c r="F22" s="31" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2253,17 +2319,18 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="10">
-    <x:mergeCell ref="B1:M1"/>
-    <x:mergeCell ref="B2:M2"/>
+  <x:mergeCells count="11">
+    <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B14:F14"/>
-    <x:mergeCell ref="B15:E15"/>
-    <x:mergeCell ref="B16:E16"/>
+    <x:mergeCell ref="B4:M4"/>
+    <x:mergeCell ref="B5:M5"/>
+    <x:mergeCell ref="B16:F16"/>
     <x:mergeCell ref="B17:E17"/>
     <x:mergeCell ref="B18:E18"/>
     <x:mergeCell ref="B19:E19"/>
     <x:mergeCell ref="B20:E20"/>
+    <x:mergeCell ref="B21:E21"/>
+    <x:mergeCell ref="B22:E22"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-WILLYMAY-DE-JESUS-evaluator-cache-serviceTracking-WILLYMAY-DE-JESUS-III-202501-202612.xlsx
+++ b/reports/service-tracking-report-WILLYMAY-DE-JESUS-evaluator-cache-serviceTracking-WILLYMAY-DE-JESUS-III-202501-202612.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -67,42 +67,6 @@
   </x:si>
   <x:si>
     <x:t>BY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ApplicationType}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Name}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Status}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Address}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.PermitNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ReferenceNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.DateOfFiling}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ExpirationDate}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ORNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Amount}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.DatePaid}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ORBy}}</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur</x:t>
@@ -180,7 +144,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="14">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -224,14 +188,6 @@
     <x:font>
       <x:b/>
       <x:vertAlign val="baseline"/>
-      <x:sz val="16"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
@@ -243,6 +199,21 @@
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -500,7 +471,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="27">
+  <x:cellStyleXfs count="28">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -508,16 +479,16 @@
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -529,13 +500,7 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -547,41 +512,50 @@
     <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="34">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -612,28 +586,20 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -648,55 +614,71 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1029,7 +1011,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1069,284 +1051,234 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="9" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="9" t="s">
+      <x:c r="D8" s="14" t="s"/>
+      <x:c r="E8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="9" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F8" s="9" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G8" s="9" t="s">
+      <x:c r="H8" s="15">
+        <x:v>45826.3053472222</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>45826.3053703704</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="n">
+        <x:v>1434444</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>45826.3117939815</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H8" s="9" t="s">
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="I8" s="9" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J8" s="9" t="s">
+      <x:c r="D9" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="K8" s="9" t="s">
+      <x:c r="E9" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="L8" s="9" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="M8" s="9" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="14" t="s"/>
-      <x:c r="C9" s="14" t="s"/>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s"/>
-      <x:c r="F9" s="14" t="s"/>
-      <x:c r="G9" s="14" t="s"/>
-      <x:c r="H9" s="14" t="s"/>
-      <x:c r="I9" s="14" t="s"/>
-      <x:c r="J9" s="14" t="s"/>
-      <x:c r="K9" s="14" t="s"/>
-      <x:c r="L9" s="14" t="s"/>
-      <x:c r="M9" s="14" t="s"/>
+      <x:c r="H9" s="15">
+        <x:v>45826.1308796296</x:v>
+      </x:c>
+      <x:c r="I9" s="15">
+        <x:v>45826</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>2734401</x:v>
+      </x:c>
+      <x:c r="K9" s="16" t="n">
+        <x:v>1052</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>45826.1478935185</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="17" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C10" s="17" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="D10" s="18" t="s"/>
+      <x:c r="E10" s="17" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F10" s="17" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s"/>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="G10" s="17" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>45826.3053472222</x:v>
-      </x:c>
-      <x:c r="I10" s="17">
-        <x:v>45826.3053703704</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:v>1434444</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="H10" s="19">
+        <x:v>45825.2634953704</x:v>
+      </x:c>
+      <x:c r="I10" s="19">
+        <x:v>45825.2635300926</x:v>
+      </x:c>
+      <x:c r="J10" s="18" t="n">
+        <x:v>274001</x:v>
+      </x:c>
+      <x:c r="K10" s="20" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L10" s="19">
-        <x:v>45826.3117939815</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>32</x:v>
+      <x:c r="L10" s="21">
+        <x:v>45825.2871759259</x:v>
+      </x:c>
+      <x:c r="M10" s="17" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="17" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C11" s="17" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D11" s="18" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E11" s="17" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F11" s="17" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G11" s="17" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H11" s="19">
+        <x:v>45826.1449768519</x:v>
+      </x:c>
+      <x:c r="I11" s="19">
+        <x:v>45826</x:v>
+      </x:c>
+      <x:c r="J11" s="18" t="n">
+        <x:v>1435666</x:v>
+      </x:c>
+      <x:c r="K11" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L11" s="21">
+        <x:v>45826.2821412037</x:v>
+      </x:c>
+      <x:c r="M11" s="17" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B14" s="22" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C14" s="23" t="s"/>
+      <x:c r="D14" s="23" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="24" t="s"/>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B15" s="25" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="C15" s="26" t="s"/>
+      <x:c r="D15" s="26" t="s"/>
+      <x:c r="E15" s="26" t="s"/>
+      <x:c r="F15" s="27" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F11" s="15" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="G11" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="H11" s="17">
-        <x:v>45826.1308796296</x:v>
-      </x:c>
-      <x:c r="I11" s="17">
-        <x:v>45826</x:v>
-      </x:c>
-      <x:c r="J11" s="16" t="n">
-        <x:v>2734401</x:v>
-      </x:c>
-      <x:c r="K11" s="18" t="n">
-        <x:v>1052</x:v>
-      </x:c>
-      <x:c r="L11" s="19">
-        <x:v>45826.1478935185</x:v>
-      </x:c>
-      <x:c r="M11" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="15" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C12" s="15" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D12" s="16" t="s"/>
-      <x:c r="E12" s="15" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F12" s="15" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="G12" s="15" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="H12" s="17">
-        <x:v>45825.2634953704</x:v>
-      </x:c>
-      <x:c r="I12" s="17">
-        <x:v>45825.2635300926</x:v>
-      </x:c>
-      <x:c r="J12" s="16" t="n">
-        <x:v>274001</x:v>
-      </x:c>
-      <x:c r="K12" s="18" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L12" s="19">
-        <x:v>45825.2871759259</x:v>
-      </x:c>
-      <x:c r="M12" s="15" t="s">
-        <x:v>32</x:v>
+    <x:row r="16" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B16" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C16" s="29" t="s"/>
+      <x:c r="D16" s="29" t="s"/>
+      <x:c r="E16" s="29" t="s"/>
+      <x:c r="F16" s="30" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C13" s="15" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="D13" s="16" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="E13" s="15" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F13" s="15" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="G13" s="15" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="H13" s="17">
-        <x:v>45826.1449768519</x:v>
-      </x:c>
-      <x:c r="I13" s="17">
-        <x:v>45826</x:v>
-      </x:c>
-      <x:c r="J13" s="16" t="n">
-        <x:v>1435666</x:v>
-      </x:c>
-      <x:c r="K13" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L13" s="19">
-        <x:v>45826.2821412037</x:v>
-      </x:c>
-      <x:c r="M13" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="20" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C16" s="21" t="s"/>
-      <x:c r="D16" s="21" t="s"/>
-      <x:c r="E16" s="22" t="s"/>
-      <x:c r="F16" s="22" t="s"/>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="23" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C17" s="24" t="s"/>
-      <x:c r="D17" s="24" t="s"/>
-      <x:c r="E17" s="24" t="s"/>
-      <x:c r="F17" s="25" t="s">
-        <x:v>47</x:v>
+    <x:row r="17" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B17" s="28" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C17" s="29" t="s"/>
+      <x:c r="D17" s="29" t="s"/>
+      <x:c r="E17" s="29" t="s"/>
+      <x:c r="F17" s="30" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="26" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C18" s="27" t="s"/>
-      <x:c r="D18" s="27" t="s"/>
-      <x:c r="E18" s="27" t="s"/>
-      <x:c r="F18" s="28" t="n">
+      <x:c r="B18" s="28" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C18" s="29" t="s"/>
+      <x:c r="D18" s="29" t="s"/>
+      <x:c r="E18" s="29" t="s"/>
+      <x:c r="F18" s="30" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="26" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C19" s="27" t="s"/>
-      <x:c r="D19" s="27" t="s"/>
-      <x:c r="E19" s="27" t="s"/>
-      <x:c r="F19" s="28" t="n">
+      <x:c r="B19" s="28" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C19" s="29" t="s"/>
+      <x:c r="D19" s="29" t="s"/>
+      <x:c r="E19" s="29" t="s"/>
+      <x:c r="F19" s="30" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="26" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C20" s="27" t="s"/>
-      <x:c r="D20" s="27" t="s"/>
-      <x:c r="E20" s="27" t="s"/>
-      <x:c r="F20" s="28" t="n">
-        <x:v>1</x:v>
+    <x:row r="20" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B20" s="31" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C20" s="32" t="s"/>
+      <x:c r="D20" s="32" t="s"/>
+      <x:c r="E20" s="32" t="s"/>
+      <x:c r="F20" s="33" t="n">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="26" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C21" s="27" t="s"/>
-      <x:c r="D21" s="27" t="s"/>
-      <x:c r="E21" s="27" t="s"/>
-      <x:c r="F21" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B22" s="29" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C22" s="30" t="s"/>
-      <x:c r="D22" s="30" t="s"/>
-      <x:c r="E22" s="30" t="s"/>
-      <x:c r="F22" s="31" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
+    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2324,13 +2256,13 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B16:F16"/>
+    <x:mergeCell ref="B14:F14"/>
+    <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B16:E16"/>
     <x:mergeCell ref="B17:E17"/>
     <x:mergeCell ref="B18:E18"/>
     <x:mergeCell ref="B19:E19"/>
     <x:mergeCell ref="B20:E20"/>
-    <x:mergeCell ref="B21:E21"/>
-    <x:mergeCell ref="B22:E22"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-WILLYMAY-DE-JESUS-evaluator-cache-serviceTracking-WILLYMAY-DE-JESUS-III-202501-202612.xlsx
+++ b/reports/service-tracking-report-WILLYMAY-DE-JESUS-evaluator-cache-serviceTracking-WILLYMAY-DE-JESUS-III-202501-202612.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -84,6 +84,9 @@
     <x:t>61-6-2025-1023</x:t>
   </x:si>
   <x:si>
+    <x:t>1434444</x:t>
+  </x:si>
+  <x:si>
     <x:t>MANUELITO TOLENTINO</x:t>
   </x:si>
   <x:si>
@@ -102,6 +105,9 @@
     <x:t>61-6-2025-1013</x:t>
   </x:si>
   <x:si>
+    <x:t>2734401</x:t>
+  </x:si>
+  <x:si>
     <x:t>Radiotelegraphy</x:t>
   </x:si>
   <x:si>
@@ -114,6 +120,9 @@
     <x:t>61-6-2025-1007</x:t>
   </x:si>
   <x:si>
+    <x:t>274001</x:t>
+  </x:si>
+  <x:si>
     <x:t>Retailer/Reseller Permit (RENEWAL)</x:t>
   </x:si>
   <x:si>
@@ -121,6 +130,9 @@
   </x:si>
   <x:si>
     <x:t>61-6-2025-1016</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1435666</x:t>
   </x:si>
   <x:si>
     <x:t>SUMMARY</x:t>
@@ -144,7 +156,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="14">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -213,13 +225,6 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
@@ -471,7 +476,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="28">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -512,50 +517,41 @@
     <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="34">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -603,6 +599,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -614,71 +614,55 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1059,7 +1043,7 @@
       <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s"/>
+      <x:c r="D8" s="15" t="s"/>
       <x:c r="E8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
@@ -1069,211 +1053,211 @@
       <x:c r="G8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="15">
-        <x:v>45826.3053472222</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
-        <x:v>45826.3053703704</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1434444</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="H8" s="16">
+        <x:v>45826.3053530208</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
+        <x:v>45826.3053769676</x:v>
+      </x:c>
+      <x:c r="J8" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>45826.3117939815</x:v>
+      <x:c r="L8" s="18">
+        <x:v>45826.311800463</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B9" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s">
         <x:v>23</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="s">
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>45826.1308796296</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H9" s="16">
+        <x:v>45826.1308837384</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
         <x:v>45826</x:v>
       </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>2734401</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
+      <x:c r="J9" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
         <x:v>1052</x:v>
       </x:c>
-      <x:c r="L9" s="15">
-        <x:v>45826.1478935185</x:v>
+      <x:c r="L9" s="18">
+        <x:v>45826.1478993634</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="17" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C10" s="17" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D10" s="18" t="s"/>
-      <x:c r="E10" s="17" t="s">
+      <x:c r="B10" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s"/>
+      <x:c r="E10" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F10" s="17" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="G10" s="17" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="H10" s="19">
-        <x:v>45825.2634953704</x:v>
-      </x:c>
-      <x:c r="I10" s="19">
-        <x:v>45825.2635300926</x:v>
-      </x:c>
-      <x:c r="J10" s="18" t="n">
-        <x:v>274001</x:v>
-      </x:c>
-      <x:c r="K10" s="20" t="n">
+      <x:c r="F10" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>45825.2635056481</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
+        <x:v>45825.2635335069</x:v>
+      </x:c>
+      <x:c r="J10" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L10" s="21">
-        <x:v>45825.2871759259</x:v>
-      </x:c>
-      <x:c r="M10" s="17" t="s">
-        <x:v>20</x:v>
+      <x:c r="L10" s="18">
+        <x:v>45825.2871799306</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="17" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C11" s="17" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D11" s="18" t="s">
+      <x:c r="B11" s="14" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="E11" s="17" t="s">
+      <x:c r="D11" s="15" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F11" s="17" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G11" s="17" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="H11" s="19">
-        <x:v>45826.1449768519</x:v>
-      </x:c>
-      <x:c r="I11" s="19">
+      <x:c r="F11" s="14" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>45826.1449770949</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
         <x:v>45826</x:v>
       </x:c>
-      <x:c r="J11" s="18" t="n">
-        <x:v>1435666</x:v>
-      </x:c>
-      <x:c r="K11" s="20" t="n">
+      <x:c r="J11" s="15" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L11" s="21">
-        <x:v>45826.2821412037</x:v>
-      </x:c>
-      <x:c r="M11" s="17" t="s">
-        <x:v>20</x:v>
+      <x:c r="L11" s="18">
+        <x:v>45826.2821424653</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="22" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C14" s="23" t="s"/>
-      <x:c r="D14" s="23" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="24" t="s"/>
+      <x:c r="B14" s="19" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C14" s="20" t="s"/>
+      <x:c r="D14" s="20" t="s"/>
+      <x:c r="E14" s="21" t="s"/>
+      <x:c r="F14" s="21" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="25" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C15" s="26" t="s"/>
-      <x:c r="D15" s="26" t="s"/>
-      <x:c r="E15" s="26" t="s"/>
-      <x:c r="F15" s="27" t="s">
-        <x:v>35</x:v>
+      <x:c r="B15" s="22" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C15" s="23" t="s"/>
+      <x:c r="D15" s="23" t="s"/>
+      <x:c r="E15" s="23" t="s"/>
+      <x:c r="F15" s="24" t="s">
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="28" t="s">
+      <x:c r="B16" s="25" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C16" s="29" t="s"/>
-      <x:c r="D16" s="29" t="s"/>
-      <x:c r="E16" s="29" t="s"/>
-      <x:c r="F16" s="30" t="n">
+      <x:c r="C16" s="26" t="s"/>
+      <x:c r="D16" s="26" t="s"/>
+      <x:c r="E16" s="26" t="s"/>
+      <x:c r="F16" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="28" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C17" s="29" t="s"/>
-      <x:c r="D17" s="29" t="s"/>
-      <x:c r="E17" s="29" t="s"/>
-      <x:c r="F17" s="30" t="n">
+      <x:c r="B17" s="25" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C17" s="26" t="s"/>
+      <x:c r="D17" s="26" t="s"/>
+      <x:c r="E17" s="26" t="s"/>
+      <x:c r="F17" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="28" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C18" s="29" t="s"/>
-      <x:c r="D18" s="29" t="s"/>
-      <x:c r="E18" s="29" t="s"/>
-      <x:c r="F18" s="30" t="n">
+      <x:c r="B18" s="25" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C18" s="26" t="s"/>
+      <x:c r="D18" s="26" t="s"/>
+      <x:c r="E18" s="26" t="s"/>
+      <x:c r="F18" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="28" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C19" s="29" t="s"/>
-      <x:c r="D19" s="29" t="s"/>
-      <x:c r="E19" s="29" t="s"/>
-      <x:c r="F19" s="30" t="n">
+      <x:c r="B19" s="25" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C19" s="26" t="s"/>
+      <x:c r="D19" s="26" t="s"/>
+      <x:c r="E19" s="26" t="s"/>
+      <x:c r="F19" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B20" s="31" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C20" s="32" t="s"/>
-      <x:c r="D20" s="32" t="s"/>
-      <x:c r="E20" s="32" t="s"/>
-      <x:c r="F20" s="33" t="n">
+      <x:c r="B20" s="28" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C20" s="29" t="s"/>
+      <x:c r="D20" s="29" t="s"/>
+      <x:c r="E20" s="29" t="s"/>
+      <x:c r="F20" s="30" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-WILLYMAY-DE-JESUS-evaluator-cache-serviceTracking-WILLYMAY-DE-JESUS-III-202501-202612.xlsx
+++ b/reports/service-tracking-report-WILLYMAY-DE-JESUS-evaluator-cache-serviceTracking-WILLYMAY-DE-JESUS-III-202501-202612.xlsx
@@ -995,7 +995,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1035,7 +1035,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
@@ -1072,7 +1072,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -1110,7 +1110,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
         <x:v>28</x:v>
       </x:c>
@@ -1146,7 +1146,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
         <x:v>33</x:v>
       </x:c>

--- a/reports/service-tracking-report-WILLYMAY-DE-JESUS-evaluator-cache-serviceTracking-WILLYMAY-DE-JESUS-III-202501-202612.xlsx
+++ b/reports/service-tracking-report-WILLYMAY-DE-JESUS-evaluator-cache-serviceTracking-WILLYMAY-DE-JESUS-III-202501-202612.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <x:si>
-    <x:t>EVALUATOR SUMMARY</x:t>
+    <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
   <x:si>
     <x:t>WILLYMAY DE JESUS</x:t>

--- a/reports/service-tracking-report-WILLYMAY-DE-JESUS-evaluator-cache-serviceTracking-WILLYMAY-DE-JESUS-III-202501-202612.xlsx
+++ b/reports/service-tracking-report-WILLYMAY-DE-JESUS-evaluator-cache-serviceTracking-WILLYMAY-DE-JESUS-III-202501-202612.xlsx
@@ -22,15 +22,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
   <x:si>
     <x:t>WILLYMAY DE JESUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>III | June 2025</x:t>
   </x:si>
   <x:si>
     <x:t>Application Type</x:t>
@@ -476,7 +473,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="25">
+  <x:cellStyleXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -493,6 +490,9 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -551,7 +551,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="31">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -587,6 +587,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -961,20 +965,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>45809</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -997,267 +1001,267 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="D8" s="16" t="s"/>
+      <x:c r="E8" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s"/>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="F8" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="G8" s="15" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="H8" s="17">
+        <x:v>45826.3053530208</x:v>
+      </x:c>
+      <x:c r="I8" s="17">
+        <x:v>45826.3053769676</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="16">
-        <x:v>45826.3053530208</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>45826.3053769676</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="s">
+      <x:c r="K8" s="18" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L8" s="19">
+        <x:v>45826.311800463</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="K8" s="17" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L8" s="18">
-        <x:v>45826.311800463</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
+      <x:c r="B9" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C9" s="14" t="s">
+      <x:c r="D9" s="16" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="D9" s="15" t="s">
+      <x:c r="E9" s="15" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F9" s="15" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="E9" s="14" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
+      <x:c r="G9" s="15" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="G9" s="14" t="s">
+      <x:c r="H9" s="17">
+        <x:v>45826.1308837384</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>45826</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="H9" s="16">
-        <x:v>45826.1308837384</x:v>
-      </x:c>
-      <x:c r="I9" s="16">
-        <x:v>45826</x:v>
-      </x:c>
-      <x:c r="J9" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="K9" s="17" t="n">
+      <x:c r="K9" s="18" t="n">
         <x:v>1052</x:v>
       </x:c>
-      <x:c r="L9" s="18">
+      <x:c r="L9" s="19">
         <x:v>45826.1478993634</x:v>
       </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>21</x:v>
+      <x:c r="M9" s="15" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="14" t="s">
+      <x:c r="B10" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C10" s="14" t="s">
+      <x:c r="D10" s="16" t="s"/>
+      <x:c r="E10" s="15" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="D10" s="15" t="s"/>
-      <x:c r="E10" s="14" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
+      <x:c r="G10" s="15" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="G10" s="14" t="s">
+      <x:c r="H10" s="17">
+        <x:v>45825.2635056481</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>45825.2635335069</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="H10" s="16">
-        <x:v>45825.2635056481</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>45825.2635335069</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="K10" s="17" t="n">
+      <x:c r="K10" s="18" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L10" s="18">
+      <x:c r="L10" s="19">
         <x:v>45825.2871799306</x:v>
       </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>21</x:v>
+      <x:c r="M10" s="15" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="14" t="s">
+      <x:c r="B11" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
+      <x:c r="G11" s="15" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="G11" s="14" t="s">
+      <x:c r="H11" s="17">
+        <x:v>45826.1449770949</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>45826</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="H11" s="16">
-        <x:v>45826.1449770949</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>45826</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="K11" s="17" t="n">
+      <x:c r="K11" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L11" s="18">
+      <x:c r="L11" s="19">
         <x:v>45826.2821424653</x:v>
       </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>21</x:v>
+      <x:c r="M11" s="15" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="19" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C14" s="20" t="s"/>
-      <x:c r="D14" s="20" t="s"/>
-      <x:c r="E14" s="21" t="s"/>
-      <x:c r="F14" s="21" t="s"/>
+      <x:c r="B14" s="20" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C14" s="21" t="s"/>
+      <x:c r="D14" s="21" t="s"/>
+      <x:c r="E14" s="22" t="s"/>
+      <x:c r="F14" s="22" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="22" t="s">
+      <x:c r="B15" s="23" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C15" s="24" t="s"/>
+      <x:c r="D15" s="24" t="s"/>
+      <x:c r="E15" s="24" t="s"/>
+      <x:c r="F15" s="25" t="s">
         <x:v>38</x:v>
-      </x:c>
-      <x:c r="C15" s="23" t="s"/>
-      <x:c r="D15" s="23" t="s"/>
-      <x:c r="E15" s="23" t="s"/>
-      <x:c r="F15" s="24" t="s">
-        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C16" s="26" t="s"/>
-      <x:c r="D16" s="26" t="s"/>
-      <x:c r="E16" s="26" t="s"/>
-      <x:c r="F16" s="27" t="n">
+      <x:c r="B16" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C16" s="27" t="s"/>
+      <x:c r="D16" s="27" t="s"/>
+      <x:c r="E16" s="27" t="s"/>
+      <x:c r="F16" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="25" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C17" s="26" t="s"/>
-      <x:c r="D17" s="26" t="s"/>
-      <x:c r="E17" s="26" t="s"/>
-      <x:c r="F17" s="27" t="n">
+      <x:c r="B17" s="26" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C17" s="27" t="s"/>
+      <x:c r="D17" s="27" t="s"/>
+      <x:c r="E17" s="27" t="s"/>
+      <x:c r="F17" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="25" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C18" s="26" t="s"/>
-      <x:c r="D18" s="26" t="s"/>
-      <x:c r="E18" s="26" t="s"/>
-      <x:c r="F18" s="27" t="n">
+      <x:c r="B18" s="26" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C18" s="27" t="s"/>
+      <x:c r="D18" s="27" t="s"/>
+      <x:c r="E18" s="27" t="s"/>
+      <x:c r="F18" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="25" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C19" s="26" t="s"/>
-      <x:c r="D19" s="26" t="s"/>
-      <x:c r="E19" s="26" t="s"/>
-      <x:c r="F19" s="27" t="n">
+      <x:c r="B19" s="26" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C19" s="27" t="s"/>
+      <x:c r="D19" s="27" t="s"/>
+      <x:c r="E19" s="27" t="s"/>
+      <x:c r="F19" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B20" s="28" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C20" s="29" t="s"/>
-      <x:c r="D20" s="29" t="s"/>
-      <x:c r="E20" s="29" t="s"/>
-      <x:c r="F20" s="30" t="n">
+      <x:c r="B20" s="29" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C20" s="30" t="s"/>
+      <x:c r="D20" s="30" t="s"/>
+      <x:c r="E20" s="30" t="s"/>
+      <x:c r="F20" s="31" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-WILLYMAY-DE-JESUS-evaluator-cache-serviceTracking-WILLYMAY-DE-JESUS-III-202501-202612.xlsx
+++ b/reports/service-tracking-report-WILLYMAY-DE-JESUS-evaluator-cache-serviceTracking-WILLYMAY-DE-JESUS-III-202501-202612.xlsx
@@ -153,7 +153,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -193,14 +193,6 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -473,7 +465,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -484,16 +476,13 @@
     <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -505,53 +494,53 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -586,87 +575,83 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -968,17 +953,17 @@
       <x:c r="B5" s="12">
         <x:v>45809</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1001,267 +986,267 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s"/>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="D8" s="15" t="s"/>
+      <x:c r="E8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>45826.3053530208</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>45826.3053769676</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>45826.311800463</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="E9" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>45826.1308837384</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>45826</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>1052</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>45826.1478993634</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s"/>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="D10" s="15" t="s"/>
+      <x:c r="E10" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="16">
         <x:v>45825.2635056481</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="16">
         <x:v>45825.2635335069</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="18">
         <x:v>45825.2871799306</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="D11" s="15" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="E11" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="16">
         <x:v>45826.1449770949</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="16">
         <x:v>45826</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="s">
+      <x:c r="J11" s="15" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="18">
         <x:v>45826.2821424653</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="20" t="s">
+      <x:c r="B14" s="19" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C14" s="21" t="s"/>
-      <x:c r="D14" s="21" t="s"/>
-      <x:c r="E14" s="22" t="s"/>
-      <x:c r="F14" s="22" t="s"/>
+      <x:c r="C14" s="20" t="s"/>
+      <x:c r="D14" s="20" t="s"/>
+      <x:c r="E14" s="21" t="s"/>
+      <x:c r="F14" s="21" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="23" t="s">
+      <x:c r="B15" s="22" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C15" s="24" t="s"/>
-      <x:c r="D15" s="24" t="s"/>
-      <x:c r="E15" s="24" t="s"/>
-      <x:c r="F15" s="25" t="s">
+      <x:c r="C15" s="23" t="s"/>
+      <x:c r="D15" s="23" t="s"/>
+      <x:c r="E15" s="23" t="s"/>
+      <x:c r="F15" s="24" t="s">
         <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="26" t="s">
+      <x:c r="B16" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C16" s="27" t="s"/>
-      <x:c r="D16" s="27" t="s"/>
-      <x:c r="E16" s="27" t="s"/>
-      <x:c r="F16" s="28" t="n">
+      <x:c r="C16" s="26" t="s"/>
+      <x:c r="D16" s="26" t="s"/>
+      <x:c r="E16" s="26" t="s"/>
+      <x:c r="F16" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="26" t="s">
+      <x:c r="B17" s="25" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C17" s="27" t="s"/>
-      <x:c r="D17" s="27" t="s"/>
-      <x:c r="E17" s="27" t="s"/>
-      <x:c r="F17" s="28" t="n">
+      <x:c r="C17" s="26" t="s"/>
+      <x:c r="D17" s="26" t="s"/>
+      <x:c r="E17" s="26" t="s"/>
+      <x:c r="F17" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="26" t="s">
+      <x:c r="B18" s="25" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C18" s="27" t="s"/>
-      <x:c r="D18" s="27" t="s"/>
-      <x:c r="E18" s="27" t="s"/>
-      <x:c r="F18" s="28" t="n">
+      <x:c r="C18" s="26" t="s"/>
+      <x:c r="D18" s="26" t="s"/>
+      <x:c r="E18" s="26" t="s"/>
+      <x:c r="F18" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="26" t="s">
+      <x:c r="B19" s="25" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C19" s="27" t="s"/>
-      <x:c r="D19" s="27" t="s"/>
-      <x:c r="E19" s="27" t="s"/>
-      <x:c r="F19" s="28" t="n">
+      <x:c r="C19" s="26" t="s"/>
+      <x:c r="D19" s="26" t="s"/>
+      <x:c r="E19" s="26" t="s"/>
+      <x:c r="F19" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B20" s="29" t="s">
+      <x:c r="B20" s="28" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C20" s="30" t="s"/>
-      <x:c r="D20" s="30" t="s"/>
-      <x:c r="E20" s="30" t="s"/>
-      <x:c r="F20" s="31" t="n">
+      <x:c r="C20" s="29" t="s"/>
+      <x:c r="D20" s="29" t="s"/>
+      <x:c r="E20" s="29" t="s"/>
+      <x:c r="F20" s="30" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-WILLYMAY-DE-JESUS-evaluator-cache-serviceTracking-WILLYMAY-DE-JESUS-III-202501-202612.xlsx
+++ b/reports/service-tracking-report-WILLYMAY-DE-JESUS-evaluator-cache-serviceTracking-WILLYMAY-DE-JESUS-III-202501-202612.xlsx
@@ -66,15 +66,63 @@
     <x:t>BY</x:t>
   </x:si>
   <x:si>
+    <x:t>Radiotelegraphy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANGELICA VERGARA PANCHITO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Maimpis, City Of San Fernando (Capital), Pampanga</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEMP-ROIII-1007-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-6-2025-1007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>274001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANUELITO TOLENTINO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Radio Station License (RENEWAL)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JUAN DELA CRUZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RSL-ROIII-1002-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-6-2025-1013</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2734401</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Retailer/Reseller Permit (RENEWAL)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MP-ROIII-1003-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-6-2025-1016</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1435666</x:t>
+  </x:si>
+  <x:si>
     <x:t>Amateur</x:t>
   </x:si>
   <x:si>
     <x:t>JULIETA ROBLEDO AMANTE</x:t>
   </x:si>
   <x:si>
-    <x:t>Maimpis, City Of San Fernando (Capital), Pampanga</x:t>
-  </x:si>
-  <x:si>
     <x:t>TEMP-ROIII-1018-25</x:t>
   </x:si>
   <x:si>
@@ -82,54 +130,6 @@
   </x:si>
   <x:si>
     <x:t>1434444</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANUELITO TOLENTINO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Radio Station License (RENEWAL)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JUAN DELA CRUZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RSL-ROIII-1002-25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-6-2025-1013</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2734401</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Radiotelegraphy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANGELICA VERGARA PANCHITO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEMP-ROIII-1007-25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-6-2025-1007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>274001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Retailer/Reseller Permit (RENEWAL)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MP-ROIII-1003-25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-6-2025-1016</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1435666</x:t>
   </x:si>
   <x:si>
     <x:t>SUMMARY</x:t>
@@ -1043,10 +1043,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="H8" s="16">
-        <x:v>45826.3053530208</x:v>
+        <x:v>45825.2635056481</x:v>
       </x:c>
       <x:c r="I8" s="16">
-        <x:v>45826.3053769676</x:v>
+        <x:v>45825.2635335069</x:v>
       </x:c>
       <x:c r="J8" s="15" t="s">
         <x:v>19</x:v>
@@ -1055,7 +1055,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="L8" s="18">
-        <x:v>45826.311800463</x:v>
+        <x:v>45825.2871799306</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
         <x:v>20</x:v>
@@ -1104,32 +1104,34 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C10" s="14" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s"/>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
+        <x:v>23</x:v>
+      </x:c>
       <x:c r="E10" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="F10" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="G10" s="14" t="s">
+      <x:c r="H10" s="16">
+        <x:v>45826.1449770949</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
+        <x:v>45826</x:v>
+      </x:c>
+      <x:c r="J10" s="15" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="H10" s="16">
-        <x:v>45825.2635056481</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>45825.2635335069</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="s">
-        <x:v>31</x:v>
-      </x:c>
       <x:c r="K10" s="17" t="n">
-        <x:v>50</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L10" s="18">
-        <x:v>45825.2871799306</x:v>
+        <x:v>45826.2821424653</x:v>
       </x:c>
       <x:c r="M10" s="14" t="s">
         <x:v>20</x:v>
@@ -1137,14 +1139,12 @@
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>23</x:v>
-      </x:c>
+      <x:c r="D11" s="15" t="s"/>
       <x:c r="E11" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
@@ -1155,19 +1155,19 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="H11" s="16">
-        <x:v>45826.1449770949</x:v>
+        <x:v>45826.3053530208</x:v>
       </x:c>
       <x:c r="I11" s="16">
-        <x:v>45826</x:v>
+        <x:v>45826.3053769676</x:v>
       </x:c>
       <x:c r="J11" s="15" t="s">
         <x:v>35</x:v>
       </x:c>
       <x:c r="K11" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="L11" s="18">
-        <x:v>45826.2821424653</x:v>
+        <x:v>45826.311800463</x:v>
       </x:c>
       <x:c r="M11" s="14" t="s">
         <x:v>20</x:v>
@@ -1197,7 +1197,7 @@
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
       <x:c r="B16" s="25" t="s">
-        <x:v>14</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C16" s="26" t="s"/>
       <x:c r="D16" s="26" t="s"/>
@@ -1219,7 +1219,7 @@
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
       <x:c r="B18" s="25" t="s">
-        <x:v>27</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C18" s="26" t="s"/>
       <x:c r="D18" s="26" t="s"/>
@@ -1230,7 +1230,7 @@
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
       <x:c r="B19" s="25" t="s">
-        <x:v>32</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C19" s="26" t="s"/>
       <x:c r="D19" s="26" t="s"/>
